--- a/InputData/elec/WUbPPT/Water Use by Power Plant Type.xlsx
+++ b/InputData/elec/WUbPPT/Water Use by Power Plant Type.xlsx
@@ -1,36 +1,129 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI - units progress\InputData\elec\WUbPPT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\WUbPPT\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930F802E-37E3-4899-BDB6-7DC3DEFD7DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13500"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Generation" sheetId="4" r:id="rId2"/>
-    <sheet name="Water Withdrawals" sheetId="2" r:id="rId3"/>
-    <sheet name="Water Consumption" sheetId="3" r:id="rId4"/>
+    <sheet name="Generation" sheetId="2" r:id="rId2"/>
+    <sheet name="Water Withdrawals" sheetId="3" r:id="rId3"/>
+    <sheet name="Water Consumption" sheetId="4" r:id="rId4"/>
     <sheet name="2015 Consolidated Data" sheetId="5" r:id="rId5"/>
     <sheet name="WUbPPT-withdrawals" sheetId="6" r:id="rId6"/>
-    <sheet name="WUbPPT-consumption" sheetId="8" r:id="rId7"/>
+    <sheet name="WUbPPT-consumption" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="97">
+  <si>
+    <t>WUbPPT Water Use by Power Plant Type</t>
+  </si>
+  <si>
+    <t>Iowa</t>
+  </si>
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>Joint Global Change Research Institute / Pacific Northwest National Laboratory</t>
+  </si>
+  <si>
+    <t>GCAM model v5.1.2</t>
+  </si>
+  <si>
+    <t>http://www.globalchange.umd.edu/gcam/</t>
+  </si>
+  <si>
+    <t>Reference scenario, energy &gt; energy transformation &gt; electricity &gt; elec gen by gen tech, elec water withdrawals by gen tech, elec water consumption by gen tech</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>GCAM has data for water withdrawals (water taken to use for cooling) and</t>
+  </si>
+  <si>
+    <t>for water consumption (water taken and not returned to the water body -</t>
+  </si>
+  <si>
+    <t>i.e. evaporated).  Most power plant cooling water is discharged back to</t>
+  </si>
+  <si>
+    <t>the water body at a higher temperature, which is why withdrawals are</t>
+  </si>
+  <si>
+    <t>much larger than consumption.</t>
+  </si>
+  <si>
+    <t>For hydroelectric plants, GCAM has no value for withdrawals, but has</t>
+  </si>
+  <si>
+    <t>a value for consumption.  We assume the consumption value is</t>
+  </si>
+  <si>
+    <t>the amount of water that evaporates off the surface of the reservoir</t>
+  </si>
+  <si>
+    <t>created by the dam, which otherwise would not have had a chance</t>
+  </si>
+  <si>
+    <t>to evaporate before flowing downriver.  We assume it has no water</t>
+  </si>
+  <si>
+    <t>withdrawals because the reservoir is considered a part of the</t>
+  </si>
+  <si>
+    <t>water system.</t>
+  </si>
+  <si>
+    <t>Conversion Factors</t>
+  </si>
+  <si>
+    <t>liters per cubic km</t>
+  </si>
+  <si>
+    <t>MWh per EJ</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>subsector</t>
+  </si>
+  <si>
+    <t>technology</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
   <si>
     <t>Reference,date=2018-28-11T14:16:43-08:00</t>
   </si>
@@ -38,135 +131,120 @@
     <t>USA</t>
   </si>
   <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t>biomass (IGCC)</t>
+  </si>
+  <si>
+    <t>EJ</t>
+  </si>
+  <si>
+    <t>biomass (conv)</t>
+  </si>
+  <si>
+    <t>biomass cogen</t>
+  </si>
+  <si>
+    <t>coal</t>
+  </si>
+  <si>
+    <t>coal (IGCC)</t>
+  </si>
+  <si>
+    <t>coal (conv pul)</t>
+  </si>
+  <si>
+    <t>coal cogen</t>
+  </si>
+  <si>
+    <t>gas</t>
+  </si>
+  <si>
+    <t>gas (CC)</t>
+  </si>
+  <si>
+    <t>gas (steam/CT)</t>
+  </si>
+  <si>
+    <t>gas cogen</t>
+  </si>
+  <si>
+    <t>geothermal</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>hydrogen</t>
+  </si>
+  <si>
+    <t>hydrogen cogen</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>Gen_III</t>
+  </si>
+  <si>
+    <t>Gen_II_LWR</t>
+  </si>
+  <si>
+    <t>refined liquids</t>
+  </si>
+  <si>
+    <t>refined liquids (CC)</t>
+  </si>
+  <si>
+    <t>refined liquids (steam/CT)</t>
+  </si>
+  <si>
+    <t>refined liquids cogen</t>
+  </si>
+  <si>
+    <t>rooftop_pv</t>
+  </si>
+  <si>
+    <t>solar</t>
+  </si>
+  <si>
+    <t>CSP</t>
+  </si>
+  <si>
+    <t>CSP_storage</t>
+  </si>
+  <si>
+    <t>PV</t>
+  </si>
+  <si>
+    <t>PV_storage</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>wind_storage</t>
+  </si>
+  <si>
+    <t>sector</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
     <t>electricity</t>
   </si>
   <si>
-    <t>biomass</t>
-  </si>
-  <si>
-    <t>biomass (IGCC)</t>
-  </si>
-  <si>
     <t>water_td_elec_W</t>
   </si>
   <si>
     <t>km^3</t>
   </si>
   <si>
-    <t>biomass (conv)</t>
-  </si>
-  <si>
-    <t>coal</t>
-  </si>
-  <si>
-    <t>coal (IGCC)</t>
-  </si>
-  <si>
-    <t>coal (conv pul)</t>
-  </si>
-  <si>
-    <t>gas</t>
-  </si>
-  <si>
-    <t>gas (CC)</t>
-  </si>
-  <si>
-    <t>gas (steam/CT)</t>
-  </si>
-  <si>
-    <t>geothermal</t>
-  </si>
-  <si>
-    <t>nuclear</t>
-  </si>
-  <si>
-    <t>Gen_III</t>
-  </si>
-  <si>
-    <t>Gen_II_LWR</t>
-  </si>
-  <si>
-    <t>refined liquids</t>
-  </si>
-  <si>
-    <t>refined liquids (CC)</t>
-  </si>
-  <si>
-    <t>refined liquids (steam/CT)</t>
-  </si>
-  <si>
-    <t>solar</t>
-  </si>
-  <si>
-    <t>CSP</t>
-  </si>
-  <si>
-    <t>CSP_storage</t>
-  </si>
-  <si>
-    <t>PV</t>
-  </si>
-  <si>
-    <t>PV_storage</t>
-  </si>
-  <si>
     <t>water_td_elec_C</t>
   </si>
   <si>
-    <t>hydro</t>
-  </si>
-  <si>
-    <t>EJ</t>
-  </si>
-  <si>
-    <t>biomass cogen</t>
-  </si>
-  <si>
-    <t>coal cogen</t>
-  </si>
-  <si>
-    <t>gas cogen</t>
-  </si>
-  <si>
-    <t>hydrogen</t>
-  </si>
-  <si>
-    <t>hydrogen cogen</t>
-  </si>
-  <si>
-    <t>refined liquids cogen</t>
-  </si>
-  <si>
-    <t>rooftop_pv</t>
-  </si>
-  <si>
-    <t>wind</t>
-  </si>
-  <si>
-    <t>wind_storage</t>
-  </si>
-  <si>
-    <t>scenario</t>
-  </si>
-  <si>
-    <t>region</t>
-  </si>
-  <si>
-    <t>subsector</t>
-  </si>
-  <si>
-    <t>technology</t>
-  </si>
-  <si>
-    <t>Units</t>
-  </si>
-  <si>
-    <t>sector</t>
-  </si>
-  <si>
-    <t>input</t>
-  </si>
-  <si>
     <t>Generation (EJ)</t>
   </si>
   <si>
@@ -182,46 +260,25 @@
     <t>Water Consumption per Unit Generation (km^3/EJ)</t>
   </si>
   <si>
-    <t>Conversion Factors</t>
-  </si>
-  <si>
-    <t>MWh per EJ</t>
-  </si>
-  <si>
     <t>Water Withdrawals per Unit Generation (l/MWh)</t>
   </si>
   <si>
     <t>Water Consumption per Unit Generation (l/MWh)</t>
   </si>
   <si>
-    <t>liters per cubic km</t>
-  </si>
-  <si>
-    <t>WUbPPT Water Use by Power Plant Type</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>GCAM model v5.1.2</t>
-  </si>
-  <si>
-    <t>http://www.globalchange.umd.edu/gcam/</t>
-  </si>
-  <si>
-    <t>Joint Global Change Research Institute / Pacific Northwest National Laboratory</t>
-  </si>
-  <si>
-    <t>Reference scenario, energy &gt; energy transformation &gt; electricity &gt; elec gen by gen tech, elec water withdrawals by gen tech, elec water consumption by gen tech</t>
+    <t>Unit: liters/(MW*hour)</t>
+  </si>
+  <si>
+    <t>Water demand</t>
   </si>
   <si>
     <t>hard coal</t>
   </si>
   <si>
-    <t>natural gas nonpeaker</t>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
   </si>
   <si>
     <t>onshore wind</t>
@@ -245,42 +302,6 @@
     <t>offshore wind</t>
   </si>
   <si>
-    <t>GCAM has data for water withdrawals (water taken to use for cooling) and</t>
-  </si>
-  <si>
-    <t>for water consumption (water taken and not returned to the water body -</t>
-  </si>
-  <si>
-    <t>i.e. evaporated).  Most power plant cooling water is discharged back to</t>
-  </si>
-  <si>
-    <t>the water body at a higher temperature, which is why withdrawals are</t>
-  </si>
-  <si>
-    <t>much larger than consumption.</t>
-  </si>
-  <si>
-    <t>For hydroelectric plants, GCAM has no value for withdrawals, but has</t>
-  </si>
-  <si>
-    <t>a value for consumption.  We assume the consumption value is</t>
-  </si>
-  <si>
-    <t>the amount of water that evaporates off the surface of the reservoir</t>
-  </si>
-  <si>
-    <t>created by the dam, which otherwise would not have had a chance</t>
-  </si>
-  <si>
-    <t>to evaporate before flowing downriver.  We assume it has no water</t>
-  </si>
-  <si>
-    <t>withdrawals because the reservoir is considered a part of the</t>
-  </si>
-  <si>
-    <t>water system.</t>
-  </si>
-  <si>
     <t>crude oil</t>
   </si>
   <si>
@@ -290,17 +311,32 @@
     <t>municipal solid waste</t>
   </si>
   <si>
-    <t>Water withdrawals (liters/(MW*hour))</t>
-  </si>
-  <si>
-    <t>Water consumption (liters/(MW*hour))</t>
+    <t>hard coal w CCS</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle w CCS</t>
+  </si>
+  <si>
+    <t>biomass w CCS</t>
+  </si>
+  <si>
+    <t>lignite w CCS</t>
+  </si>
+  <si>
+    <t>small modular reactor</t>
+  </si>
+  <si>
+    <t>hydrogen combustion turbine</t>
+  </si>
+  <si>
+    <t>hydrogen combined cycle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,6 +356,29 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -350,9 +409,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -373,6 +432,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -654,166 +718,169 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="7">
         <v>2018</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>10^12</f>
         <v>1000000000000</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>277777777.77777702</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z25"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="18.3984375" customWidth="1"/>
-    <col min="4" max="4" width="27.3984375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E1" s="2">
         <v>1990</v>
@@ -879,21 +946,21 @@
         <v>2100</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -959,21 +1026,21 @@
         <v>0.34978900000000002</v>
       </c>
       <c r="Z2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E3">
         <v>7.9134899999999994E-2</v>
@@ -1039,21 +1106,21 @@
         <v>0.30399399999999999</v>
       </c>
       <c r="Z3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E4">
         <v>0.22271299999999999</v>
@@ -1119,21 +1186,21 @@
         <v>0.187585</v>
       </c>
       <c r="Z4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>0</v>
-      </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1199,21 +1266,21 @@
         <v>3.5587300000000002</v>
       </c>
       <c r="Z5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>0</v>
-      </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E6">
         <v>6.0290900000000001</v>
@@ -1279,21 +1346,21 @@
         <v>10.87</v>
       </c>
       <c r="Z6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>8.9847099999999999E-2</v>
@@ -1359,21 +1426,21 @@
         <v>0.139098</v>
       </c>
       <c r="Z7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>0</v>
-      </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E8">
         <v>0.59030000000000005</v>
@@ -1439,21 +1506,21 @@
         <v>4.0196699999999996</v>
       </c>
       <c r="Z8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>0</v>
-      </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="E9">
         <v>0.43599500000000002</v>
@@ -1519,21 +1586,21 @@
         <v>0.14057500000000001</v>
       </c>
       <c r="Z9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>0</v>
-      </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E10">
         <v>0.35644199999999998</v>
@@ -1599,21 +1666,21 @@
         <v>0.30209000000000003</v>
       </c>
       <c r="Z10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>0</v>
-      </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E11">
         <v>5.7645599999999998E-2</v>
@@ -1679,21 +1746,21 @@
         <v>0.71600299999999995</v>
       </c>
       <c r="Z11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>0</v>
-      </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E12">
         <v>0.98334699999999997</v>
@@ -1759,21 +1826,21 @@
         <v>1.04634</v>
       </c>
       <c r="Z12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>0</v>
-      </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1839,21 +1906,21 @@
         <v>3.14831E-2</v>
       </c>
       <c r="Z13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>0</v>
-      </c>
       <c r="B14" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1919,21 +1986,21 @@
         <v>4.0533299999999999</v>
       </c>
       <c r="Z14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>0</v>
-      </c>
       <c r="B15" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="E15">
         <v>2.20139</v>
@@ -1999,21 +2066,21 @@
         <v>0</v>
       </c>
       <c r="Z15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>0</v>
-      </c>
       <c r="B16" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2079,21 +2146,21 @@
         <v>0.122679</v>
       </c>
       <c r="Z16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>0</v>
-      </c>
       <c r="B17" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="E17">
         <v>0.45076699999999997</v>
@@ -2159,21 +2226,21 @@
         <v>5.2327800000000002E-3</v>
       </c>
       <c r="Z17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>0</v>
-      </c>
       <c r="B18" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E18">
         <v>1.9592499999999999E-2</v>
@@ -2239,21 +2306,21 @@
         <v>3.0210399999999998E-2</v>
       </c>
       <c r="Z18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>0</v>
-      </c>
       <c r="B19" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2319,21 +2386,21 @@
         <v>5.0576799999999998E-2</v>
       </c>
       <c r="Z19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>0</v>
-      </c>
       <c r="B20" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="E20">
         <v>2.3869E-3</v>
@@ -2399,21 +2466,21 @@
         <v>2.7512399999999999E-2</v>
       </c>
       <c r="Z20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>0</v>
-      </c>
       <c r="B21" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2479,21 +2546,21 @@
         <v>0.30076000000000003</v>
       </c>
       <c r="Z21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>0</v>
-      </c>
       <c r="B22" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="E22" s="1">
         <v>1.0800400000000001E-5</v>
@@ -2559,21 +2626,21 @@
         <v>0.49257239999999902</v>
       </c>
       <c r="Z22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>0</v>
-      </c>
       <c r="B23" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2639,21 +2706,21 @@
         <v>4.4284629999999997E-3</v>
       </c>
       <c r="Z23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>0</v>
-      </c>
       <c r="B24" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E24">
         <v>1.10381E-2</v>
@@ -2719,21 +2786,21 @@
         <v>2.8700709999999998</v>
       </c>
       <c r="Z24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>0</v>
-      </c>
       <c r="B25" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2799,7 +2866,7 @@
         <v>1.6823399999999999E-2</v>
       </c>
       <c r="Z25" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2808,34 +2875,34 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AB16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" customWidth="1"/>
-    <col min="3" max="3" width="12.73046875" customWidth="1"/>
-    <col min="4" max="4" width="15.59765625" customWidth="1"/>
-    <col min="5" max="5" width="29.265625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="29.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G1" s="2">
         <v>1990</v>
@@ -2901,27 +2968,27 @@
         <v>2100</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2987,27 +3054,27 @@
         <v>0.12786110199999901</v>
       </c>
       <c r="AB2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>0.69392854000000004</v>
@@ -3073,27 +3140,27 @@
         <v>0.15418430999999999</v>
       </c>
       <c r="AB3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3159,27 +3226,27 @@
         <v>1.3248231829999999</v>
       </c>
       <c r="AB4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>110.27552193</v>
@@ -3245,27 +3312,27 @@
         <v>25.970151419999901</v>
       </c>
       <c r="AB5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>0.67783796999999901</v>
@@ -3331,27 +3398,27 @@
         <v>1.2859827099999901</v>
       </c>
       <c r="AB6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>3.8073925999999898</v>
@@ -3417,27 +3484,27 @@
         <v>6.2147147999999999E-2</v>
       </c>
       <c r="AB7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G8">
         <v>6.9623000000000004E-2</v>
@@ -3503,27 +3570,27 @@
         <v>1.0086651600000001</v>
       </c>
       <c r="AB8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="F9" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3589,27 +3656,27 @@
         <v>7.1137269999999999</v>
       </c>
       <c r="AB9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="F10" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G10">
         <v>38.676989999999897</v>
@@ -3675,27 +3742,27 @@
         <v>0</v>
       </c>
       <c r="AB10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -3761,27 +3828,27 @@
         <v>1.3921205640000001</v>
       </c>
       <c r="AB11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="F12" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>3.9937057</v>
@@ -3847,27 +3914,27 @@
         <v>3.5751641000000001E-3</v>
       </c>
       <c r="AB12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F13" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G13">
         <v>1.33932E-3</v>
@@ -3933,27 +4000,27 @@
         <v>2.52174656782999E-2</v>
       </c>
       <c r="AB13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F14" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -4019,27 +4086,27 @@
         <v>0.27567077370999998</v>
       </c>
       <c r="AB14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F15" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G15" s="1">
         <v>6.0002999999999998E-8</v>
@@ -4105,27 +4172,27 @@
         <v>2.7365339999999901E-3</v>
       </c>
       <c r="AB15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -4191,7 +4258,7 @@
         <v>2.4602769999999999E-5</v>
       </c>
       <c r="AB16" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4200,34 +4267,34 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AB17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.59765625" customWidth="1"/>
-    <col min="4" max="4" width="17.1328125" customWidth="1"/>
-    <col min="5" max="5" width="27.73046875" customWidth="1"/>
-    <col min="6" max="6" width="18.86328125" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" customWidth="1"/>
+    <col min="5" max="5" width="27.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G1" s="2">
         <v>1990</v>
@@ -4293,27 +4360,27 @@
         <v>2100</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -4379,27 +4446,27 @@
         <v>0.121749522</v>
       </c>
       <c r="AB2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>1.7264350000000001E-2</v>
@@ -4465,27 +4532,27 @@
         <v>9.7061778000000001E-2</v>
       </c>
       <c r="AB3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -4551,27 +4618,27 @@
         <v>1.260898283</v>
       </c>
       <c r="AB4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G5">
         <v>3.1418712099999899</v>
@@ -4637,27 +4704,27 @@
         <v>6.9712168400000003</v>
       </c>
       <c r="AB5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>0.10108934999999999</v>
@@ -4723,27 +4790,27 @@
         <v>0.449319202999999</v>
       </c>
       <c r="AB6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G7">
         <v>8.9163800000000001E-2</v>
@@ -4809,27 +4876,27 @@
         <v>4.1457725000000001E-2</v>
       </c>
       <c r="AB7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G8">
         <v>6.9623000000000004E-2</v>
@@ -4895,27 +4962,27 @@
         <v>1.0086651600000001</v>
       </c>
       <c r="AB8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G9">
         <v>4.64358</v>
@@ -4981,27 +5048,27 @@
         <v>4.9410299999999996</v>
       </c>
       <c r="AB9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -5067,27 +5134,27 @@
         <v>2.5219843000000002</v>
       </c>
       <c r="AB10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G11">
         <v>1.0302370000000001</v>
@@ -5153,27 +5220,27 @@
         <v>0</v>
       </c>
       <c r="AB11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -5239,27 +5306,27 @@
         <v>1.6948847600000001E-2</v>
       </c>
       <c r="AB12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G13">
         <v>0.1271708</v>
@@ -5325,27 +5392,27 @@
         <v>2.4593980999999998E-3</v>
       </c>
       <c r="AB13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>1.33932E-3</v>
@@ -5411,27 +5478,27 @@
         <v>2.52174656782999E-2</v>
       </c>
       <c r="AB14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -5497,27 +5564,27 @@
         <v>0.27567077370999998</v>
       </c>
       <c r="AB15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F16" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G16" s="1">
         <v>6.0002999999999998E-8</v>
@@ -5583,27 +5650,27 @@
         <v>2.7365339999999901E-3</v>
       </c>
       <c r="AB16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="F17" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -5669,57 +5736,57 @@
         <v>2.4602769999999999E-5</v>
       </c>
       <c r="AB17" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="18.59765625" customWidth="1"/>
-    <col min="3" max="3" width="27.265625" customWidth="1"/>
-    <col min="4" max="4" width="27.3984375" customWidth="1"/>
-    <col min="5" max="5" width="29.265625" customWidth="1"/>
-    <col min="6" max="8" width="28.59765625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" customWidth="1"/>
+    <col min="5" max="5" width="29.28515625" customWidth="1"/>
+    <col min="6" max="8" width="28.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="B2">
         <f>VLOOKUP($A2,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5734,11 +5801,11 @@
         <v>0</v>
       </c>
       <c r="E2" s="5" t="str">
-        <f>IFERROR(C2/$B2,"")</f>
+        <f t="shared" ref="E2:E17" si="0">IFERROR(C2/$B2,"")</f>
         <v/>
       </c>
       <c r="F2" s="5" t="str">
-        <f>IFERROR(D2/$B2,"")</f>
+        <f t="shared" ref="F2:F17" si="1">IFERROR(D2/$B2,"")</f>
         <v/>
       </c>
       <c r="G2" s="6" t="str">
@@ -5750,9 +5817,9 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <f>VLOOKUP($A3,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5767,11 +5834,11 @@
         <v>1.7976895999999899E-2</v>
       </c>
       <c r="E3" s="5">
-        <f t="shared" ref="E3:E17" si="0">IFERROR(C3/$B3,"")</f>
+        <f t="shared" si="0"/>
         <v>3.8585237382374893</v>
       </c>
       <c r="F3" s="5">
-        <f t="shared" ref="F3:F17" si="1">IFERROR(D3/$B3,"")</f>
+        <f t="shared" si="1"/>
         <v>0.26992620042552845</v>
       </c>
       <c r="G3" s="6">
@@ -5783,9 +5850,9 @@
         <v>971.73432153190504</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <f>VLOOKUP($A4,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5816,9 +5883,9 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <f>VLOOKUP($A5,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5849,9 +5916,9 @@
         <v>1960.1218806510001</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <f>VLOOKUP($A6,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5882,9 +5949,9 @@
         <v>620.64013917559782</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <f>VLOOKUP($A7,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5915,9 +5982,9 @@
         <v>745.03641899418494</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <f>VLOOKUP($A8,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5948,9 +6015,9 @@
         <v>4930.3337614825323</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <f>VLOOKUP($A9,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5977,9 +6044,9 @@
         <v>16999.982182329317</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="B10">
         <f>VLOOKUP($A10,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6010,9 +6077,9 @@
         <v>2226.6884419345611</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B11">
         <f>VLOOKUP($A11,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6043,9 +6110,9 @@
         <v>1684.774202794702</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="B12">
         <f>VLOOKUP($A12,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6076,9 +6143,9 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="B13">
         <f>VLOOKUP($A13,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6109,9 +6176,9 @@
         <v>1183.8566612430841</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="B14">
         <f>VLOOKUP($A14,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6142,9 +6209,9 @@
         <v>2103.5281074696754</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="B15">
         <f>VLOOKUP($A15,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6175,9 +6242,9 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="B16">
         <f>VLOOKUP($A16,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6208,9 +6275,9 @@
         <v>20.000187272534593</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="B17">
         <f>VLOOKUP($A17,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6247,326 +6314,477 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
-    <tabColor theme="8" tint="-0.249977111117893"/>
+    <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.265625" customWidth="1"/>
-    <col min="2" max="2" width="18.265625" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="B1" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B2" s="6">
         <f>'2015 Consolidated Data'!G5</f>
         <v>54577.83755331373</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="B3" s="6">
+        <f>'2015 Consolidated Data'!G7</f>
+        <v>30331.387156235895</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="6">
         <f>'2015 Consolidated Data'!G6</f>
         <v>4159.9245358989992</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="6">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="6">
         <f>'2015 Consolidated Data'!G11</f>
         <v>63249.562164099065</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="6">
         <f>'2015 Consolidated Data'!G9</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="6">
+        <v>80</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="6">
         <f>'2015 Consolidated Data'!G16</f>
         <v>20.000187272534593</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="6">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="6">
         <f>'2015 Consolidated Data'!G14</f>
         <v>2103.5281074696754</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="6">
         <f>'2015 Consolidated Data'!G3</f>
         <v>13890.685457654999</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="6">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="6">
         <f>'2015 Consolidated Data'!G8</f>
         <v>4930.3337614825323</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="6">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="6">
         <f>'2015 Consolidated Data'!G13</f>
         <v>23313.172724314474</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="6">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="6">
         <f>'2015 Consolidated Data'!G7</f>
         <v>30331.387156235895</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="6">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="6">
         <f>'2015 Consolidated Data'!G5</f>
         <v>54577.83755331373</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="6">
-        <f>B11</f>
+        <v>86</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="6">
+        <f>B12</f>
         <v>23313.172724314474</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="6">
-        <f>B11</f>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="6">
+        <f>B12</f>
         <v>23313.172724314474</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="6">
-        <f>B9</f>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="6">
+        <f>B10</f>
         <v>13890.685457654999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="6">
+        <f>B2</f>
+        <v>54577.83755331373</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="6">
+        <f>B4</f>
+        <v>4159.9245358989992</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" s="6">
+        <f>B10</f>
+        <v>13890.685457654999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="6">
+        <f>B14</f>
+        <v>54577.83755331373</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="6">
+        <f>B5</f>
+        <v>63249.562164099065</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="6">
+        <f>B13</f>
+        <v>30331.387156235895</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="6">
+        <f>B4</f>
+        <v>4159.9245358989992</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
-    <tabColor theme="8" tint="-0.249977111117893"/>
+    <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.265625" customWidth="1"/>
-    <col min="2" max="2" width="18.265625" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>75</v>
+      </c>
       <c r="B1" s="10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B2" s="6">
         <f>'2015 Consolidated Data'!H5</f>
         <v>1960.1218806510001</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="B3" s="6">
+        <f>'2015 Consolidated Data'!H7</f>
+        <v>745.03641899418494</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="6">
         <f>'2015 Consolidated Data'!H6</f>
         <v>620.64013917559782</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="6">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="6">
         <f>'2015 Consolidated Data'!H11</f>
         <v>1684.774202794702</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="6">
         <f>'2015 Consolidated Data'!H9</f>
         <v>16999.982182329317</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="6">
+        <v>80</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="6">
         <f>'2015 Consolidated Data'!H16</f>
         <v>20.000187272534593</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="6">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="6">
         <f>'2015 Consolidated Data'!H14</f>
         <v>2103.5281074696754</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="6">
         <f>'2015 Consolidated Data'!H3</f>
         <v>971.73432153190504</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="6">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="6">
         <f>'2015 Consolidated Data'!H8</f>
         <v>4930.3337614825323</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="6">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="6">
         <f>'2015 Consolidated Data'!H13</f>
         <v>1183.8566612430841</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="6">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="6">
         <f>'2015 Consolidated Data'!H7</f>
         <v>745.03641899418494</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="6">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="6">
         <f>'2015 Consolidated Data'!H5</f>
         <v>1960.1218806510001</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="6">
-        <f>B11</f>
+        <v>86</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="6">
+        <f>B12</f>
         <v>1183.8566612430841</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="6">
-        <f>B11</f>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="6">
+        <f>B12</f>
         <v>1183.8566612430841</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="6">
-        <f>B9</f>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="6">
+        <f>B10</f>
         <v>971.73432153190504</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="6">
+        <f>B2</f>
+        <v>1960.1218806510001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="6">
+        <f>B4</f>
+        <v>620.64013917559782</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" s="6">
+        <f>B10</f>
+        <v>971.73432153190504</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="6">
+        <f>B14</f>
+        <v>1960.1218806510001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="6">
+        <f>B5</f>
+        <v>1684.774202794702</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="6">
+        <f>B13</f>
+        <v>745.03641899418494</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="6">
+        <f>B4</f>
+        <v>620.64013917559782</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/elec/WUbPPT/Water Use by Power Plant Type.xlsx
+++ b/InputData/elec/WUbPPT/Water Use by Power Plant Type.xlsx
@@ -1,28 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\WUbPPT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\WUbPPT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930F802E-37E3-4899-BDB6-7DC3DEFD7DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABAB2E8-C7B5-485C-A73C-3C2E68CFD24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Generation" sheetId="2" r:id="rId2"/>
-    <sheet name="Water Withdrawals" sheetId="3" r:id="rId3"/>
-    <sheet name="Water Consumption" sheetId="4" r:id="rId4"/>
+    <sheet name="Generation" sheetId="4" r:id="rId2"/>
+    <sheet name="Water Withdrawals" sheetId="2" r:id="rId3"/>
+    <sheet name="Water Consumption" sheetId="3" r:id="rId4"/>
     <sheet name="2015 Consolidated Data" sheetId="5" r:id="rId5"/>
     <sheet name="WUbPPT-withdrawals" sheetId="6" r:id="rId6"/>
-    <sheet name="WUbPPT-consumption" sheetId="7" r:id="rId7"/>
+    <sheet name="WUbPPT-consumption" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,7 +34,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,30 +41,216 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="96">
+  <si>
+    <t>Reference,date=2018-28-11T14:16:43-08:00</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>electricity</t>
+  </si>
+  <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t>biomass (IGCC)</t>
+  </si>
+  <si>
+    <t>water_td_elec_W</t>
+  </si>
+  <si>
+    <t>km^3</t>
+  </si>
+  <si>
+    <t>biomass (conv)</t>
+  </si>
+  <si>
+    <t>coal</t>
+  </si>
+  <si>
+    <t>coal (IGCC)</t>
+  </si>
+  <si>
+    <t>coal (conv pul)</t>
+  </si>
+  <si>
+    <t>gas</t>
+  </si>
+  <si>
+    <t>gas (CC)</t>
+  </si>
+  <si>
+    <t>gas (steam/CT)</t>
+  </si>
+  <si>
+    <t>geothermal</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>Gen_III</t>
+  </si>
+  <si>
+    <t>Gen_II_LWR</t>
+  </si>
+  <si>
+    <t>refined liquids</t>
+  </si>
+  <si>
+    <t>refined liquids (CC)</t>
+  </si>
+  <si>
+    <t>refined liquids (steam/CT)</t>
+  </si>
+  <si>
+    <t>solar</t>
+  </si>
+  <si>
+    <t>CSP</t>
+  </si>
+  <si>
+    <t>CSP_storage</t>
+  </si>
+  <si>
+    <t>PV</t>
+  </si>
+  <si>
+    <t>PV_storage</t>
+  </si>
+  <si>
+    <t>water_td_elec_C</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>EJ</t>
+  </si>
+  <si>
+    <t>biomass cogen</t>
+  </si>
+  <si>
+    <t>coal cogen</t>
+  </si>
+  <si>
+    <t>gas cogen</t>
+  </si>
+  <si>
+    <t>hydrogen</t>
+  </si>
+  <si>
+    <t>hydrogen cogen</t>
+  </si>
+  <si>
+    <t>refined liquids cogen</t>
+  </si>
+  <si>
+    <t>rooftop_pv</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>wind_storage</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>subsector</t>
+  </si>
+  <si>
+    <t>technology</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>sector</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>Generation (EJ)</t>
+  </si>
+  <si>
+    <t>Water Withdrawals (km^3)</t>
+  </si>
+  <si>
+    <t>Water Consumption (km^3)</t>
+  </si>
+  <si>
+    <t>Water Withdrawals per Unit Generation (km^3/EJ)</t>
+  </si>
+  <si>
+    <t>Water Consumption per Unit Generation (km^3/EJ)</t>
+  </si>
+  <si>
+    <t>Conversion Factors</t>
+  </si>
+  <si>
+    <t>MWh per EJ</t>
+  </si>
+  <si>
+    <t>Water Withdrawals per Unit Generation (l/MWh)</t>
+  </si>
+  <si>
+    <t>Water Consumption per Unit Generation (l/MWh)</t>
+  </si>
+  <si>
+    <t>liters per cubic km</t>
+  </si>
   <si>
     <t>WUbPPT Water Use by Power Plant Type</t>
   </si>
   <si>
-    <t>Iowa</t>
-  </si>
-  <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>GCAM model v5.1.2</t>
+  </si>
+  <si>
+    <t>http://www.globalchange.umd.edu/gcam/</t>
+  </si>
+  <si>
     <t>Joint Global Change Research Institute / Pacific Northwest National Laboratory</t>
   </si>
   <si>
-    <t>GCAM model v5.1.2</t>
-  </si>
-  <si>
-    <t>http://www.globalchange.umd.edu/gcam/</t>
-  </si>
-  <si>
     <t>Reference scenario, energy &gt; energy transformation &gt; electricity &gt; elec gen by gen tech, elec water withdrawals by gen tech, elec water consumption by gen tech</t>
   </si>
   <si>
-    <t>Notes</t>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>onshore wind</t>
+  </si>
+  <si>
+    <t>solar PV</t>
+  </si>
+  <si>
+    <t>solar thermal</t>
+  </si>
+  <si>
+    <t>petroleum</t>
+  </si>
+  <si>
+    <t>natural gas peaker</t>
+  </si>
+  <si>
+    <t>lignite</t>
+  </si>
+  <si>
+    <t>offshore wind</t>
   </si>
   <si>
     <t>GCAM has data for water withdrawals (water taken to use for cooling) and</t>
@@ -101,214 +289,25 @@
     <t>water system.</t>
   </si>
   <si>
-    <t>Conversion Factors</t>
-  </si>
-  <si>
-    <t>liters per cubic km</t>
-  </si>
-  <si>
-    <t>MWh per EJ</t>
-  </si>
-  <si>
-    <t>scenario</t>
-  </si>
-  <si>
-    <t>region</t>
-  </si>
-  <si>
-    <t>subsector</t>
-  </si>
-  <si>
-    <t>technology</t>
-  </si>
-  <si>
-    <t>Units</t>
-  </si>
-  <si>
-    <t>Reference,date=2018-28-11T14:16:43-08:00</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
-  <si>
-    <t>biomass</t>
-  </si>
-  <si>
-    <t>biomass (IGCC)</t>
-  </si>
-  <si>
-    <t>EJ</t>
-  </si>
-  <si>
-    <t>biomass (conv)</t>
-  </si>
-  <si>
-    <t>biomass cogen</t>
-  </si>
-  <si>
-    <t>coal</t>
-  </si>
-  <si>
-    <t>coal (IGCC)</t>
-  </si>
-  <si>
-    <t>coal (conv pul)</t>
-  </si>
-  <si>
-    <t>coal cogen</t>
-  </si>
-  <si>
-    <t>gas</t>
-  </si>
-  <si>
-    <t>gas (CC)</t>
-  </si>
-  <si>
-    <t>gas (steam/CT)</t>
-  </si>
-  <si>
-    <t>gas cogen</t>
-  </si>
-  <si>
-    <t>geothermal</t>
-  </si>
-  <si>
-    <t>hydro</t>
-  </si>
-  <si>
-    <t>hydrogen</t>
-  </si>
-  <si>
-    <t>hydrogen cogen</t>
-  </si>
-  <si>
-    <t>nuclear</t>
-  </si>
-  <si>
-    <t>Gen_III</t>
-  </si>
-  <si>
-    <t>Gen_II_LWR</t>
-  </si>
-  <si>
-    <t>refined liquids</t>
-  </si>
-  <si>
-    <t>refined liquids (CC)</t>
-  </si>
-  <si>
-    <t>refined liquids (steam/CT)</t>
-  </si>
-  <si>
-    <t>refined liquids cogen</t>
-  </si>
-  <si>
-    <t>rooftop_pv</t>
-  </si>
-  <si>
-    <t>solar</t>
-  </si>
-  <si>
-    <t>CSP</t>
-  </si>
-  <si>
-    <t>CSP_storage</t>
-  </si>
-  <si>
-    <t>PV</t>
-  </si>
-  <si>
-    <t>PV_storage</t>
-  </si>
-  <si>
-    <t>wind</t>
-  </si>
-  <si>
-    <t>wind_storage</t>
-  </si>
-  <si>
-    <t>sector</t>
-  </si>
-  <si>
-    <t>input</t>
-  </si>
-  <si>
-    <t>electricity</t>
-  </si>
-  <si>
-    <t>water_td_elec_W</t>
-  </si>
-  <si>
-    <t>km^3</t>
-  </si>
-  <si>
-    <t>water_td_elec_C</t>
-  </si>
-  <si>
-    <t>Generation (EJ)</t>
-  </si>
-  <si>
-    <t>Water Withdrawals (km^3)</t>
-  </si>
-  <si>
-    <t>Water Consumption (km^3)</t>
-  </si>
-  <si>
-    <t>Water Withdrawals per Unit Generation (km^3/EJ)</t>
-  </si>
-  <si>
-    <t>Water Consumption per Unit Generation (km^3/EJ)</t>
-  </si>
-  <si>
-    <t>Water Withdrawals per Unit Generation (l/MWh)</t>
-  </si>
-  <si>
-    <t>Water Consumption per Unit Generation (l/MWh)</t>
+    <t>crude oil</t>
+  </si>
+  <si>
+    <t>heavy or residual fuel oil</t>
+  </si>
+  <si>
+    <t>municipal solid waste</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
   </si>
   <si>
     <t>Unit: liters/(MW*hour)</t>
   </si>
   <si>
     <t>Water demand</t>
-  </si>
-  <si>
-    <t>hard coal</t>
-  </si>
-  <si>
-    <t>natural gas steam turbine</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle</t>
-  </si>
-  <si>
-    <t>onshore wind</t>
-  </si>
-  <si>
-    <t>solar PV</t>
-  </si>
-  <si>
-    <t>solar thermal</t>
-  </si>
-  <si>
-    <t>petroleum</t>
-  </si>
-  <si>
-    <t>natural gas peaker</t>
-  </si>
-  <si>
-    <t>lignite</t>
-  </si>
-  <si>
-    <t>offshore wind</t>
-  </si>
-  <si>
-    <t>crude oil</t>
-  </si>
-  <si>
-    <t>heavy or residual fuel oil</t>
-  </si>
-  <si>
-    <t>municipal solid waste</t>
   </si>
   <si>
     <t>hard coal w CCS</t>
@@ -409,7 +408,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -727,18 +726,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -748,92 +744,92 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
@@ -844,7 +840,7 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -871,16 +867,16 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E1" s="2">
         <v>1990</v>
@@ -946,21 +942,21 @@
         <v>2100</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1026,21 +1022,21 @@
         <v>0.34978900000000002</v>
       </c>
       <c r="Z2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="E3">
         <v>7.9134899999999994E-2</v>
@@ -1106,21 +1102,21 @@
         <v>0.30399399999999999</v>
       </c>
       <c r="Z3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
         <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
       </c>
       <c r="E4">
         <v>0.22271299999999999</v>
@@ -1186,21 +1182,21 @@
         <v>0.187585</v>
       </c>
       <c r="Z4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1266,21 +1262,21 @@
         <v>3.5587300000000002</v>
       </c>
       <c r="Z5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>6.0290900000000001</v>
@@ -1346,21 +1342,21 @@
         <v>10.87</v>
       </c>
       <c r="Z6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E7">
         <v>8.9847099999999999E-2</v>
@@ -1426,21 +1422,21 @@
         <v>0.139098</v>
       </c>
       <c r="Z7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E8">
         <v>0.59030000000000005</v>
@@ -1506,21 +1502,21 @@
         <v>4.0196699999999996</v>
       </c>
       <c r="Z8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="E9">
         <v>0.43599500000000002</v>
@@ -1586,21 +1582,21 @@
         <v>0.14057500000000001</v>
       </c>
       <c r="Z9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E10">
         <v>0.35644199999999998</v>
@@ -1666,21 +1662,21 @@
         <v>0.30209000000000003</v>
       </c>
       <c r="Z10" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="E11">
         <v>5.7645599999999998E-2</v>
@@ -1746,21 +1742,21 @@
         <v>0.71600299999999995</v>
       </c>
       <c r="Z11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E12">
         <v>0.98334699999999997</v>
@@ -1826,21 +1822,21 @@
         <v>1.04634</v>
       </c>
       <c r="Z12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1906,21 +1902,21 @@
         <v>3.14831E-2</v>
       </c>
       <c r="Z13" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1986,21 +1982,21 @@
         <v>4.0533299999999999</v>
       </c>
       <c r="Z14" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E15">
         <v>2.20139</v>
@@ -2066,21 +2062,21 @@
         <v>0</v>
       </c>
       <c r="Z15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2146,21 +2142,21 @@
         <v>0.122679</v>
       </c>
       <c r="Z16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="E17">
         <v>0.45076699999999997</v>
@@ -2226,21 +2222,21 @@
         <v>5.2327800000000002E-3</v>
       </c>
       <c r="Z17" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E18">
         <v>1.9592499999999999E-2</v>
@@ -2306,21 +2302,21 @@
         <v>3.0210399999999998E-2</v>
       </c>
       <c r="Z18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2386,21 +2382,21 @@
         <v>5.0576799999999998E-2</v>
       </c>
       <c r="Z19" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="E20">
         <v>2.3869E-3</v>
@@ -2466,21 +2462,21 @@
         <v>2.7512399999999999E-2</v>
       </c>
       <c r="Z20" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2546,21 +2542,21 @@
         <v>0.30076000000000003</v>
       </c>
       <c r="Z21" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="E22" s="1">
         <v>1.0800400000000001E-5</v>
@@ -2626,21 +2622,21 @@
         <v>0.49257239999999902</v>
       </c>
       <c r="Z22" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="D23" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2706,21 +2702,21 @@
         <v>4.4284629999999997E-3</v>
       </c>
       <c r="Z23" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="E24">
         <v>1.10381E-2</v>
@@ -2786,21 +2782,21 @@
         <v>2.8700709999999998</v>
       </c>
       <c r="Z24" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2866,7 +2862,7 @@
         <v>1.6823399999999999E-2</v>
       </c>
       <c r="Z25" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2887,22 +2883,22 @@
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="G1" s="2">
         <v>1990</v>
@@ -2968,27 +2964,27 @@
         <v>2100</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -3054,27 +3050,27 @@
         <v>0.12786110199999901</v>
       </c>
       <c r="AB2" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="G3">
         <v>0.69392854000000004</v>
@@ -3140,27 +3136,27 @@
         <v>0.15418430999999999</v>
       </c>
       <c r="AB3" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3226,27 +3222,27 @@
         <v>1.3248231829999999</v>
       </c>
       <c r="AB4" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>110.27552193</v>
@@ -3312,27 +3308,27 @@
         <v>25.970151419999901</v>
       </c>
       <c r="AB5" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>0.67783796999999901</v>
@@ -3398,27 +3394,27 @@
         <v>1.2859827099999901</v>
       </c>
       <c r="AB6" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>3.8073925999999898</v>
@@ -3484,27 +3480,27 @@
         <v>6.2147147999999999E-2</v>
       </c>
       <c r="AB7" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="G8">
         <v>6.9623000000000004E-2</v>
@@ -3570,27 +3566,27 @@
         <v>1.0086651600000001</v>
       </c>
       <c r="AB8" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3656,27 +3652,27 @@
         <v>7.1137269999999999</v>
       </c>
       <c r="AB9" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>38.676989999999897</v>
@@ -3742,27 +3738,27 @@
         <v>0</v>
       </c>
       <c r="AB10" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -3828,27 +3824,27 @@
         <v>1.3921205640000001</v>
       </c>
       <c r="AB11" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="G12">
         <v>3.9937057</v>
@@ -3914,27 +3910,27 @@
         <v>3.5751641000000001E-3</v>
       </c>
       <c r="AB12" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="G13">
         <v>1.33932E-3</v>
@@ -4000,27 +3996,27 @@
         <v>2.52174656782999E-2</v>
       </c>
       <c r="AB13" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -4086,27 +4082,27 @@
         <v>0.27567077370999998</v>
       </c>
       <c r="AB14" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1">
         <v>6.0002999999999998E-8</v>
@@ -4172,27 +4168,27 @@
         <v>2.7365339999999901E-3</v>
       </c>
       <c r="AB15" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -4258,7 +4254,7 @@
         <v>2.4602769999999999E-5</v>
       </c>
       <c r="AB16" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4279,22 +4275,22 @@
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="G1" s="2">
         <v>1990</v>
@@ -4360,27 +4356,27 @@
         <v>2100</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -4446,27 +4442,27 @@
         <v>0.121749522</v>
       </c>
       <c r="AB2" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G3">
         <v>1.7264350000000001E-2</v>
@@ -4532,27 +4528,27 @@
         <v>9.7061778000000001E-2</v>
       </c>
       <c r="AB3" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -4618,27 +4614,27 @@
         <v>1.260898283</v>
       </c>
       <c r="AB4" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G5">
         <v>3.1418712099999899</v>
@@ -4704,27 +4700,27 @@
         <v>6.9712168400000003</v>
       </c>
       <c r="AB5" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G6">
         <v>0.10108934999999999</v>
@@ -4790,27 +4786,27 @@
         <v>0.449319202999999</v>
       </c>
       <c r="AB6" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G7">
         <v>8.9163800000000001E-2</v>
@@ -4876,27 +4872,27 @@
         <v>4.1457725000000001E-2</v>
       </c>
       <c r="AB7" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G8">
         <v>6.9623000000000004E-2</v>
@@ -4962,27 +4958,27 @@
         <v>1.0086651600000001</v>
       </c>
       <c r="AB8" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G9">
         <v>4.64358</v>
@@ -5048,27 +5044,27 @@
         <v>4.9410299999999996</v>
       </c>
       <c r="AB9" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -5134,27 +5130,27 @@
         <v>2.5219843000000002</v>
       </c>
       <c r="AB10" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G11">
         <v>1.0302370000000001</v>
@@ -5220,27 +5216,27 @@
         <v>0</v>
       </c>
       <c r="AB11" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -5306,27 +5302,27 @@
         <v>1.6948847600000001E-2</v>
       </c>
       <c r="AB12" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G13">
         <v>0.1271708</v>
@@ -5392,27 +5388,27 @@
         <v>2.4593980999999998E-3</v>
       </c>
       <c r="AB13" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G14">
         <v>1.33932E-3</v>
@@ -5478,27 +5474,27 @@
         <v>2.52174656782999E-2</v>
       </c>
       <c r="AB14" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -5564,27 +5560,27 @@
         <v>0.27567077370999998</v>
       </c>
       <c r="AB15" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G16" s="1">
         <v>6.0002999999999998E-8</v>
@@ -5650,27 +5646,27 @@
         <v>2.7365339999999901E-3</v>
       </c>
       <c r="AB16" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -5736,12 +5732,12 @@
         <v>2.4602769999999999E-5</v>
       </c>
       <c r="AB17" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5758,35 +5754,35 @@
     <col min="6" max="8" width="28.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <f>VLOOKUP($A2,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5801,11 +5797,11 @@
         <v>0</v>
       </c>
       <c r="E2" s="5" t="str">
-        <f t="shared" ref="E2:E17" si="0">IFERROR(C2/$B2,"")</f>
+        <f>IFERROR(C2/$B2,"")</f>
         <v/>
       </c>
       <c r="F2" s="5" t="str">
-        <f t="shared" ref="F2:F17" si="1">IFERROR(D2/$B2,"")</f>
+        <f>IFERROR(D2/$B2,"")</f>
         <v/>
       </c>
       <c r="G2" s="6" t="str">
@@ -5819,7 +5815,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <f>VLOOKUP($A3,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5834,11 +5830,11 @@
         <v>1.7976895999999899E-2</v>
       </c>
       <c r="E3" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E3:E17" si="0">IFERROR(C3/$B3,"")</f>
         <v>3.8585237382374893</v>
       </c>
       <c r="F3" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="F3:F17" si="1">IFERROR(D3/$B3,"")</f>
         <v>0.26992620042552845</v>
       </c>
       <c r="G3" s="6">
@@ -5852,7 +5848,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <f>VLOOKUP($A4,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5885,7 +5881,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <f>VLOOKUP($A5,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5918,7 +5914,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <f>VLOOKUP($A6,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5951,7 +5947,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <f>VLOOKUP($A7,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -5984,7 +5980,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <f>VLOOKUP($A8,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6017,7 +6013,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B9">
         <f>VLOOKUP($A9,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6046,7 +6042,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <f>VLOOKUP($A10,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6079,7 +6075,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="B11">
         <f>VLOOKUP($A11,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6112,7 +6108,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <f>VLOOKUP($A12,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6145,7 +6141,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <f>VLOOKUP($A13,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6178,7 +6174,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="B14">
         <f>VLOOKUP($A14,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6211,7 +6207,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <f>VLOOKUP($A15,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6244,7 +6240,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <f>VLOOKUP($A16,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6277,7 +6273,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <f>VLOOKUP($A17,Generation!$D$1:$H$25,5,FALSE)</f>
@@ -6327,15 +6323,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B2" s="6">
         <f>'2015 Consolidated Data'!G5</f>
@@ -6344,7 +6340,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B3" s="6">
         <f>'2015 Consolidated Data'!G7</f>
@@ -6353,7 +6349,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B4" s="6">
         <f>'2015 Consolidated Data'!G6</f>
@@ -6362,7 +6358,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="B5" s="6">
         <f>'2015 Consolidated Data'!G11</f>
@@ -6371,7 +6367,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B6" s="6">
         <f>'2015 Consolidated Data'!G9</f>
@@ -6380,7 +6376,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -6388,7 +6384,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="B8" s="6">
         <f>'2015 Consolidated Data'!G16</f>
@@ -6397,7 +6393,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="B9" s="6">
         <f>'2015 Consolidated Data'!G14</f>
@@ -6406,7 +6402,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="B10" s="6">
         <f>'2015 Consolidated Data'!G3</f>
@@ -6415,7 +6411,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="B11" s="6">
         <f>'2015 Consolidated Data'!G8</f>
@@ -6424,7 +6420,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B12" s="6">
         <f>'2015 Consolidated Data'!G13</f>
@@ -6433,7 +6429,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B13" s="6">
         <f>'2015 Consolidated Data'!G7</f>
@@ -6442,7 +6438,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B14" s="6">
         <f>'2015 Consolidated Data'!G5</f>
@@ -6451,7 +6447,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -6459,7 +6455,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B16" s="6">
         <f>B12</f>
@@ -6468,7 +6464,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B17" s="6">
         <f>B12</f>
@@ -6477,7 +6473,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B18" s="6">
         <f>B10</f>
@@ -6486,7 +6482,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B19" s="6">
         <f>B2</f>
@@ -6495,7 +6491,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B20" s="6">
         <f>B4</f>
@@ -6504,7 +6500,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B21" s="6">
         <f>B10</f>
@@ -6513,7 +6509,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B22" s="6">
         <f>B14</f>
@@ -6522,7 +6518,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B23" s="6">
         <f>B5</f>
@@ -6531,7 +6527,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B24" s="6">
         <f>B13</f>
@@ -6540,7 +6536,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B25" s="6">
         <f>B4</f>
@@ -6549,7 +6545,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6567,15 +6563,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B2" s="6">
         <f>'2015 Consolidated Data'!H5</f>
@@ -6584,7 +6580,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B3" s="6">
         <f>'2015 Consolidated Data'!H7</f>
@@ -6593,7 +6589,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B4" s="6">
         <f>'2015 Consolidated Data'!H6</f>
@@ -6602,7 +6598,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="B5" s="6">
         <f>'2015 Consolidated Data'!H11</f>
@@ -6611,7 +6607,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B6" s="6">
         <f>'2015 Consolidated Data'!H9</f>
@@ -6620,7 +6616,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -6628,7 +6624,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="B8" s="6">
         <f>'2015 Consolidated Data'!H16</f>
@@ -6637,7 +6633,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="B9" s="6">
         <f>'2015 Consolidated Data'!H14</f>
@@ -6646,7 +6642,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="B10" s="6">
         <f>'2015 Consolidated Data'!H3</f>
@@ -6655,7 +6651,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="B11" s="6">
         <f>'2015 Consolidated Data'!H8</f>
@@ -6664,7 +6660,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B12" s="6">
         <f>'2015 Consolidated Data'!H13</f>
@@ -6673,7 +6669,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B13" s="6">
         <f>'2015 Consolidated Data'!H7</f>
@@ -6682,7 +6678,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B14" s="6">
         <f>'2015 Consolidated Data'!H5</f>
@@ -6691,7 +6687,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -6699,7 +6695,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B16" s="6">
         <f>B12</f>
@@ -6708,7 +6704,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B17" s="6">
         <f>B12</f>
@@ -6717,7 +6713,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B18" s="6">
         <f>B10</f>
@@ -6726,7 +6722,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B19" s="6">
         <f>B2</f>
@@ -6735,7 +6731,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B20" s="6">
         <f>B4</f>
@@ -6744,7 +6740,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B21" s="6">
         <f>B10</f>
@@ -6753,7 +6749,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B22" s="6">
         <f>B14</f>
@@ -6762,7 +6758,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B23" s="6">
         <f>B5</f>
@@ -6771,7 +6767,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B24" s="6">
         <f>B13</f>
@@ -6780,7 +6776,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B25" s="6">
         <f>B4</f>
